--- a/database/event/4443/event_4443_evp_summary.xlsx
+++ b/database/event/4443/event_4443_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.2029</v>
+        <v>9.9001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8513</v>
+        <v>6.2945</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2964</v>
+        <v>3.5003</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2029</v>
+        <v>9.9001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6598</v>
+        <v>3.357</v>
       </c>
       <c r="G2" t="n">
         <v>6.5431</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6598</v>
+        <v>3.357</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6598</v>
+        <v>3.357</v>
       </c>
       <c r="J2" t="n">
         <v>7.0794</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>9.7392</v>
+        <v>10.4364</v>
       </c>
       <c r="N2" t="n">
         <v>382</v>
@@ -538,461 +538,461 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0712</v>
+        <v>5.9722</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2243</v>
+        <v>3.7972</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6273</v>
+        <v>1.9354</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0712</v>
+        <v>5.9722</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3054</v>
+        <v>2.3269</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7658</v>
+        <v>3.6453</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3054</v>
+        <v>2.3269</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3054</v>
+        <v>2.3269</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7658</v>
+        <v>3.6453</v>
       </c>
       <c r="K3" t="n">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="L3" t="n">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0712</v>
+        <v>5.972200000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>351</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0698</v>
+        <v>5.1959</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2234</v>
+        <v>3.3036</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6267</v>
+        <v>1.6261</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0698</v>
+        <v>5.1959</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4245</v>
+        <v>1.4301</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6453</v>
+        <v>3.7658</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4245</v>
+        <v>1.4301</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4245</v>
+        <v>1.4301</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6453</v>
+        <v>3.7658</v>
       </c>
       <c r="K4" t="n">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="L4" t="n">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>5.069800000000001</v>
+        <v>5.1959</v>
       </c>
       <c r="N4" t="n">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.986</v>
+        <v>5.0539</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1701</v>
+        <v>3.2133</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5929</v>
+        <v>1.5696</v>
       </c>
       <c r="E5" t="n">
-        <v>4.986</v>
+        <v>5.0539</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4082</v>
+        <v>4.5222</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5778</v>
+        <v>0.5317</v>
       </c>
       <c r="H5" t="n">
-        <v>4.609</v>
+        <v>4.7878</v>
       </c>
       <c r="I5" t="n">
-        <v>4.652</v>
+        <v>4.8281</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5778</v>
+        <v>0.5317</v>
       </c>
       <c r="K5" t="n">
-        <v>278</v>
+        <v>218</v>
       </c>
       <c r="L5" t="n">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2298</v>
+        <v>5.3598</v>
       </c>
       <c r="N5" t="n">
-        <v>390</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8081</v>
+        <v>4.9641</v>
       </c>
       <c r="C6" t="n">
-        <v>3.057</v>
+        <v>3.1562</v>
       </c>
       <c r="D6" t="n">
-        <v>1.521</v>
+        <v>1.5338</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8081</v>
+        <v>4.9641</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2764</v>
+        <v>4.3863</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5317</v>
+        <v>0.5778</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4024</v>
+        <v>4.5747</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4229</v>
+        <v>4.652</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5317</v>
+        <v>0.5778</v>
       </c>
       <c r="K6" t="n">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9546</v>
+        <v>5.2298</v>
       </c>
       <c r="N6" t="n">
-        <v>271</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5446</v>
+        <v>4.8806</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8895</v>
+        <v>3.1031</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4146</v>
+        <v>1.5005</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5446</v>
+        <v>4.8806</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8452</v>
+        <v>2.0747</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6994</v>
+        <v>2.8059</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8452</v>
+        <v>2.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8452</v>
+        <v>2.0747</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6994</v>
+        <v>2.8059</v>
       </c>
       <c r="K7" t="n">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="L7" t="n">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5446</v>
+        <v>4.880599999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4846</v>
+        <v>4.5446</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8513</v>
+        <v>2.8895</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3903</v>
+        <v>1.3667</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4846</v>
+        <v>4.5446</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0408</v>
+        <v>0.8452</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4438</v>
+        <v>3.6994</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0408</v>
+        <v>0.8452</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0408</v>
+        <v>0.8452</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4438</v>
+        <v>3.6994</v>
       </c>
       <c r="K8" t="n">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="L8" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4846</v>
+        <v>4.5446</v>
       </c>
       <c r="N8" t="n">
-        <v>249</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4535</v>
+        <v>4.4846</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8316</v>
+        <v>2.8513</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3778</v>
+        <v>1.3428</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4535</v>
+        <v>4.4846</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6476</v>
+        <v>2.0408</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8059</v>
+        <v>2.4438</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6476</v>
+        <v>2.0408</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6476</v>
+        <v>2.0408</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8059</v>
+        <v>2.4438</v>
       </c>
       <c r="K9" t="n">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="L9" t="n">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4535</v>
+        <v>4.4846</v>
       </c>
       <c r="N9" t="n">
-        <v>351</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3884</v>
+        <v>4.3871</v>
       </c>
       <c r="C10" t="n">
-        <v>2.7902</v>
+        <v>2.7893</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3515</v>
+        <v>1.3039</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3884</v>
+        <v>4.3871</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1722</v>
+        <v>1.6487</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2162</v>
+        <v>2.7384</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2389</v>
+        <v>1.6487</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2784</v>
+        <v>1.6487</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2162</v>
+        <v>2.7384</v>
       </c>
       <c r="K10" t="n">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="L10" t="n">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4946</v>
+        <v>4.3871</v>
       </c>
       <c r="N10" t="n">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.3871</v>
+        <v>4.3805</v>
       </c>
       <c r="C11" t="n">
-        <v>2.7893</v>
+        <v>2.7851</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3509</v>
+        <v>1.3013</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3871</v>
+        <v>4.3805</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6487</v>
+        <v>3.5005</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7384</v>
+        <v>0.88</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6487</v>
+        <v>3.5005</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6487</v>
+        <v>3.5005</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7384</v>
+        <v>0.88</v>
       </c>
       <c r="K11" t="n">
-        <v>235</v>
+        <v>144</v>
       </c>
       <c r="L11" t="n">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3871</v>
+        <v>4.380500000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>382</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.2124</v>
+        <v>4.3682</v>
       </c>
       <c r="C12" t="n">
-        <v>2.6783</v>
+        <v>2.7773</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2804</v>
+        <v>1.2964</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2124</v>
+        <v>4.3682</v>
       </c>
       <c r="F12" t="n">
-        <v>4.3124</v>
+        <v>4.152</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1</v>
+        <v>0.2162</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4588</v>
+        <v>4.2073</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4795</v>
+        <v>4.2784</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1</v>
+        <v>0.2162</v>
       </c>
       <c r="K12" t="n">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="L12" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3795</v>
+        <v>4.4946</v>
       </c>
       <c r="N12" t="n">
-        <v>281</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.0732</v>
+        <v>4.2504</v>
       </c>
       <c r="C13" t="n">
-        <v>2.5898</v>
+        <v>2.7024</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2241</v>
+        <v>1.2494</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0732</v>
+        <v>4.2504</v>
       </c>
       <c r="F13" t="n">
-        <v>3.9047</v>
+        <v>4.0819</v>
       </c>
       <c r="G13" t="n">
         <v>0.1685</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9047</v>
+        <v>4.0974</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9229</v>
+        <v>4.1319</v>
       </c>
       <c r="J13" t="n">
         <v>0.1685</v>
@@ -1035,7 +1035,7 @@
         <v>64</v>
       </c>
       <c r="M13" t="n">
-        <v>4.0914</v>
+        <v>4.3004</v>
       </c>
       <c r="N13" t="n">
         <v>281</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.0678</v>
+        <v>4.2223</v>
       </c>
       <c r="C14" t="n">
-        <v>2.5863</v>
+        <v>2.6846</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2219</v>
+        <v>1.2383</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0678</v>
+        <v>4.2223</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0211</v>
+        <v>4.3223</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0467</v>
+        <v>-0.1</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0211</v>
+        <v>4.4743</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0306</v>
+        <v>4.5119</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0467</v>
+        <v>-0.1</v>
       </c>
       <c r="K14" t="n">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="L14" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="M14" t="n">
-        <v>4.0773</v>
+        <v>4.4119</v>
       </c>
       <c r="N14" t="n">
-        <v>390</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5015</v>
+        <v>4.0602</v>
       </c>
       <c r="C15" t="n">
-        <v>2.2263</v>
+        <v>2.5815</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9932</v>
+        <v>1.1737</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5015</v>
+        <v>4.0602</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6215</v>
+        <v>1.0135</v>
       </c>
       <c r="G15" t="n">
-        <v>0.88</v>
+        <v>3.0467</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6215</v>
+        <v>1.0135</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6215</v>
+        <v>1.0306</v>
       </c>
       <c r="J15" t="n">
-        <v>0.88</v>
+        <v>3.0467</v>
       </c>
       <c r="K15" t="n">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="L15" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5015</v>
+        <v>4.0773</v>
       </c>
       <c r="N15" t="n">
-        <v>222</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.2634</v>
+        <v>3.2981</v>
       </c>
       <c r="C16" t="n">
-        <v>2.0749</v>
+        <v>2.097</v>
       </c>
       <c r="D16" t="n">
-        <v>0.897</v>
+        <v>0.8701</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2634</v>
+        <v>3.2981</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1583</v>
+        <v>3.193</v>
       </c>
       <c r="G16" t="n">
         <v>0.1051</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1583</v>
+        <v>3.193</v>
       </c>
       <c r="I16" t="n">
-        <v>3.173</v>
+        <v>3.2199</v>
       </c>
       <c r="J16" t="n">
         <v>0.1051</v>
@@ -1173,7 +1173,7 @@
         <v>64</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2781</v>
+        <v>3.325</v>
       </c>
       <c r="N16" t="n">
         <v>281</v>
@@ -1192,7 +1192,7 @@
         <v>2.0062</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8132</v>
       </c>
       <c r="E17" t="n">
         <v>3.1554</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4858</v>
+        <v>2.9052</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5805</v>
+        <v>1.8471</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5828</v>
+        <v>0.7135</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4858</v>
+        <v>2.9052</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2882</v>
+        <v>3.3148</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8024</v>
+        <v>-0.4096</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2882</v>
+        <v>3.3148</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2882</v>
+        <v>3.3148</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8024</v>
+        <v>-0.4096</v>
       </c>
       <c r="K18" t="n">
         <v>94</v>
@@ -1265,7 +1265,7 @@
         <v>49</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4858</v>
+        <v>2.9052</v>
       </c>
       <c r="N18" t="n">
         <v>143</v>
@@ -1274,127 +1274,127 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.37</v>
+        <v>2.8562</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5069</v>
+        <v>1.816</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5361</v>
+        <v>0.694</v>
       </c>
       <c r="E19" t="n">
-        <v>2.37</v>
+        <v>2.8562</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0217</v>
+        <v>3.6586</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.8024</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0217</v>
+        <v>3.6586</v>
       </c>
       <c r="I19" t="n">
-        <v>3.0357</v>
+        <v>3.6586</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.8024</v>
       </c>
       <c r="K19" t="n">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M19" t="n">
-        <v>2.384</v>
+        <v>2.8562</v>
       </c>
       <c r="N19" t="n">
-        <v>271</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1636</v>
+        <v>2.5822</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3756</v>
+        <v>1.6418</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4527</v>
+        <v>0.5848</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1636</v>
+        <v>2.5822</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9216</v>
+        <v>2.5822</v>
       </c>
       <c r="G20" t="n">
-        <v>1.242</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9216</v>
+        <v>2.5822</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9216</v>
+        <v>2.5822</v>
       </c>
       <c r="J20" t="n">
-        <v>1.242</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="L20" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1636</v>
+        <v>2.5822</v>
       </c>
       <c r="N20" t="n">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1313</v>
+        <v>2.5599</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3551</v>
+        <v>1.6276</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4396</v>
+        <v>0.576</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1313</v>
+        <v>2.5599</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1325</v>
+        <v>3.2116</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0012</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1325</v>
+        <v>3.2116</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1425</v>
+        <v>3.2387</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0012</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>218</v>
@@ -1403,7 +1403,7 @@
         <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1413</v>
+        <v>2.587</v>
       </c>
       <c r="N21" t="n">
         <v>271</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1207</v>
+        <v>2.4186</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3484</v>
+        <v>1.5378</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4354</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1207</v>
+        <v>2.4186</v>
       </c>
       <c r="F22" t="n">
-        <v>1.839</v>
+        <v>2.1369</v>
       </c>
       <c r="G22" t="n">
         <v>0.2817</v>
       </c>
       <c r="H22" t="n">
-        <v>1.839</v>
+        <v>2.1369</v>
       </c>
       <c r="I22" t="n">
-        <v>1.839</v>
+        <v>2.1369</v>
       </c>
       <c r="J22" t="n">
         <v>0.2817</v>
@@ -1449,7 +1449,7 @@
         <v>115</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1207</v>
+        <v>2.4186</v>
       </c>
       <c r="N22" t="n">
         <v>249</v>
@@ -1458,265 +1458,265 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.986</v>
+        <v>2.405</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2627</v>
+        <v>1.5291</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3809</v>
+        <v>0.5142</v>
       </c>
       <c r="E23" t="n">
-        <v>1.986</v>
+        <v>2.405</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5293</v>
+        <v>2.4062</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4567</v>
+        <v>-0.0012</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5293</v>
+        <v>2.4062</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5293</v>
+        <v>2.4264</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4567</v>
+        <v>-0.0012</v>
       </c>
       <c r="K23" t="n">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="L23" t="n">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="M23" t="n">
-        <v>1.986</v>
+        <v>2.4252</v>
       </c>
       <c r="N23" t="n">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9351</v>
+        <v>2.319</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2303</v>
+        <v>1.4744</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3604</v>
+        <v>0.48</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9351</v>
+        <v>2.319</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9351</v>
+        <v>2.1593</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1597</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9351</v>
+        <v>2.1593</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9351</v>
+        <v>2.1593</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1597</v>
       </c>
       <c r="K24" t="n">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9351</v>
+        <v>2.319</v>
       </c>
       <c r="N24" t="n">
-        <v>259</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8955</v>
+        <v>2.1643</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2052</v>
+        <v>1.3761</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3444</v>
+        <v>0.4183</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8955</v>
+        <v>2.1643</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7358</v>
+        <v>0.9223</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1597</v>
+        <v>1.242</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7358</v>
+        <v>0.9223</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7358</v>
+        <v>0.9223</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1597</v>
+        <v>1.242</v>
       </c>
       <c r="K25" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="L25" t="n">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8955</v>
+        <v>2.1643</v>
       </c>
       <c r="N25" t="n">
-        <v>222</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4649</v>
+        <v>1.986</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9314</v>
+        <v>1.2627</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1704</v>
+        <v>0.3473</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4649</v>
+        <v>1.986</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4649</v>
+        <v>0.5293</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.4567</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4649</v>
+        <v>0.5293</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4649</v>
+        <v>0.5293</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.4567</v>
       </c>
       <c r="K26" t="n">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4649</v>
+        <v>1.986</v>
       </c>
       <c r="N26" t="n">
-        <v>162</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4608</v>
+        <v>1.8382</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9288</v>
+        <v>1.1687</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1688</v>
+        <v>0.2884</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4608</v>
+        <v>1.8382</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4608</v>
+        <v>1.611</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.2272</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4608</v>
+        <v>1.611</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4608</v>
+        <v>1.6246</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.2272</v>
       </c>
       <c r="K27" t="n">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4608</v>
+        <v>1.8518</v>
       </c>
       <c r="N27" t="n">
-        <v>235</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3222</v>
+        <v>1.5186</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8407</v>
+        <v>0.9655</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1128</v>
+        <v>0.1611</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3222</v>
+        <v>1.5186</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7318</v>
+        <v>2.1798</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4096</v>
+        <v>-0.6612</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7318</v>
+        <v>2.1798</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7318</v>
+        <v>2.1798</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4096</v>
+        <v>-0.6612</v>
       </c>
       <c r="K28" t="n">
         <v>94</v>
@@ -1725,7 +1725,7 @@
         <v>49</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3222</v>
+        <v>1.5186</v>
       </c>
       <c r="N28" t="n">
         <v>143</v>
@@ -1734,737 +1734,737 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2107</v>
+        <v>1.4649</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7698</v>
+        <v>0.9314</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0677</v>
+        <v>0.1397</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2107</v>
+        <v>1.4649</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1459</v>
+        <v>1.4649</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0648</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1459</v>
+        <v>1.4649</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1459</v>
+        <v>1.4649</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0648</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="L29" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2107</v>
+        <v>1.4649</v>
       </c>
       <c r="N29" t="n">
-        <v>222</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1648</v>
+        <v>1.4608</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7406</v>
+        <v>0.9288</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0492</v>
+        <v>0.1381</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1648</v>
+        <v>1.4608</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9376</v>
+        <v>1.4608</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9376</v>
+        <v>1.4608</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.4608</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="L30" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1692</v>
+        <v>1.4608</v>
       </c>
       <c r="N30" t="n">
-        <v>281</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1595</v>
+        <v>1.3959</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7372</v>
+        <v>0.8875</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0471</v>
+        <v>0.1122</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1595</v>
+        <v>1.3959</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1595</v>
+        <v>1.3959</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1595</v>
+        <v>1.3959</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1595</v>
+        <v>1.3959</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>259</v>
+        <v>162</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1595</v>
+        <v>1.3959</v>
       </c>
       <c r="N31" t="n">
-        <v>259</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1407</v>
+        <v>1.3922</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.8852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0395</v>
+        <v>0.1107</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1407</v>
+        <v>1.3922</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5232</v>
+        <v>1.3922</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.3825</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5232</v>
+        <v>1.3922</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5232</v>
+        <v>1.3922</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3825</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="L32" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1407</v>
+        <v>1.3922</v>
       </c>
       <c r="N32" t="n">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1226</v>
+        <v>1.3767</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7138</v>
+        <v>0.8753</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0321</v>
+        <v>0.1046</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1226</v>
+        <v>1.3767</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6177</v>
+        <v>1.3767</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4951</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6177</v>
+        <v>1.3767</v>
       </c>
       <c r="I33" t="n">
-        <v>1.6252</v>
+        <v>1.3767</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4951</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="L33" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1301</v>
+        <v>1.3767</v>
       </c>
       <c r="N33" t="n">
-        <v>281</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>EspiranTo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0709</v>
+        <v>1.3458</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.8557</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0113</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0709</v>
+        <v>1.3458</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7811</v>
+        <v>1.3458</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2898</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7811</v>
+        <v>1.3458</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7884</v>
+        <v>1.3458</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2898</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="L34" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0782</v>
+        <v>1.3458</v>
       </c>
       <c r="N34" t="n">
-        <v>390</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.2107</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5605</v>
+        <v>0.7698</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0384</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.2107</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.1459</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.0648</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.1459</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.1459</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.0648</v>
       </c>
       <c r="K35" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.2107</v>
       </c>
       <c r="N35" t="n">
-        <v>148</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8475</v>
+        <v>1.163</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.079</v>
+        <v>0.0194</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8475</v>
+        <v>1.163</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8475</v>
+        <v>1.6581</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.4951</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8475</v>
+        <v>1.6581</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8475</v>
+        <v>1.6721</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.4951</v>
       </c>
       <c r="K36" t="n">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8475</v>
+        <v>1.177</v>
       </c>
       <c r="N36" t="n">
-        <v>148</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8177</v>
+        <v>1.1407</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5199</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.091</v>
+        <v>0.0105</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8177</v>
+        <v>1.1407</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8177</v>
+        <v>1.5232</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.3825</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8177</v>
+        <v>1.5232</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8177</v>
+        <v>1.5232</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.3825</v>
       </c>
       <c r="K37" t="n">
-        <v>214</v>
+        <v>144</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8177</v>
+        <v>1.1407</v>
       </c>
       <c r="N37" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7967</v>
+        <v>1.0651</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5065</v>
+        <v>0.6772</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0196</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7967</v>
+        <v>1.0651</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4579</v>
+        <v>0.7753</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6612</v>
+        <v>0.2898</v>
       </c>
       <c r="H38" t="n">
-        <v>1.4579</v>
+        <v>0.7753</v>
       </c>
       <c r="I38" t="n">
-        <v>1.4579</v>
+        <v>0.7884</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6612</v>
+        <v>0.2898</v>
       </c>
       <c r="K38" t="n">
-        <v>94</v>
+        <v>278</v>
       </c>
       <c r="L38" t="n">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7967</v>
+        <v>1.0782</v>
       </c>
       <c r="N38" t="n">
-        <v>143</v>
+        <v>390</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7542</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4795</v>
+        <v>0.5605</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1167</v>
+        <v>-0.0927</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7542</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>1.7695</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.0153</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.7695</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>1.7695</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.0153</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="L39" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7542</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>249</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7448</v>
+        <v>0.8475</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4735</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1205</v>
+        <v>-0.1063</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7448</v>
+        <v>0.8475</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7448</v>
+        <v>0.8475</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7448</v>
+        <v>0.8475</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7448</v>
+        <v>0.8475</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7448</v>
+        <v>0.8475</v>
       </c>
       <c r="N40" t="n">
-        <v>214</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.7542</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3451</v>
+        <v>0.4795</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2021</v>
+        <v>-0.1434</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.7542</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4484</v>
+        <v>1.7695</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9912</v>
+        <v>-1.0153</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4484</v>
+        <v>1.7695</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4526</v>
+        <v>1.7695</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9912</v>
+        <v>-1.0153</v>
       </c>
       <c r="K41" t="n">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="L41" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5386</v>
+        <v>0.7542</v>
       </c>
       <c r="N41" t="n">
-        <v>390</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5074</v>
+        <v>0.7448</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3226</v>
+        <v>0.4735</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2164</v>
+        <v>-0.1472</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5074</v>
+        <v>0.7448</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5074</v>
+        <v>0.7448</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5074</v>
+        <v>0.7448</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5074</v>
+        <v>0.7448</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5074</v>
+        <v>0.7448</v>
       </c>
       <c r="N42" t="n">
-        <v>162</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3612</v>
+        <v>0.6354</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2297</v>
+        <v>0.404</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2754</v>
+        <v>-0.1908</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3612</v>
+        <v>0.6354</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2649</v>
+        <v>0.6354</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0963</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2649</v>
+        <v>0.6354</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2649</v>
+        <v>0.6354</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0963</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="L43" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3612</v>
+        <v>0.6354</v>
       </c>
       <c r="N43" t="n">
-        <v>351</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2911</v>
+        <v>0.5461</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1851</v>
+        <v>0.3472</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3038</v>
+        <v>-0.2263</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2911</v>
+        <v>0.5461</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2911</v>
+        <v>-0.4451</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.9912</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2911</v>
+        <v>-0.4451</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2911</v>
+        <v>-0.4526</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.9912</v>
       </c>
       <c r="K44" t="n">
-        <v>148</v>
+        <v>278</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2911</v>
+        <v>0.5386</v>
       </c>
       <c r="N44" t="n">
-        <v>148</v>
+        <v>390</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2633</v>
+        <v>0.4576</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1674</v>
+        <v>0.2909</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.315</v>
+        <v>-0.2616</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2633</v>
+        <v>0.4576</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3973</v>
+        <v>1.5916</v>
       </c>
       <c r="G45" t="n">
         <v>-1.134</v>
       </c>
       <c r="H45" t="n">
-        <v>1.3973</v>
+        <v>1.5916</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3973</v>
+        <v>1.5916</v>
       </c>
       <c r="J45" t="n">
         <v>-1.134</v>
@@ -2507,7 +2507,7 @@
         <v>115</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2633000000000001</v>
+        <v>0.4576</v>
       </c>
       <c r="N45" t="n">
         <v>249</v>
@@ -2516,553 +2516,553 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2383</v>
+        <v>0.3895</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1515</v>
+        <v>0.2476</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3251</v>
+        <v>-0.2887</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2383</v>
+        <v>0.3895</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2383</v>
+        <v>0.3895</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2383</v>
+        <v>0.3895</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2383</v>
+        <v>0.3895</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2383</v>
+        <v>0.3895</v>
       </c>
       <c r="N46" t="n">
-        <v>148</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1479</v>
+        <v>0.3612</v>
       </c>
       <c r="C47" t="n">
-        <v>0.094</v>
+        <v>0.2297</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3616</v>
+        <v>-0.3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1479</v>
+        <v>0.3612</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1479</v>
+        <v>0.2649</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.0963</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1479</v>
+        <v>0.2649</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1479</v>
+        <v>0.2649</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.0963</v>
       </c>
       <c r="K47" t="n">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1479</v>
+        <v>0.3612</v>
       </c>
       <c r="N47" t="n">
-        <v>235</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EspiranTo</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1205</v>
+        <v>0.2911</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0766</v>
+        <v>0.1851</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3727</v>
+        <v>-0.3279</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1205</v>
+        <v>0.2911</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1205</v>
+        <v>0.2911</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1205</v>
+        <v>0.2911</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1205</v>
+        <v>0.2911</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>259</v>
+        <v>148</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1205</v>
+        <v>0.2911</v>
       </c>
       <c r="N48" t="n">
-        <v>259</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2383</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0464</v>
+        <v>0.1515</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3919</v>
+        <v>-0.349</v>
       </c>
       <c r="E49" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2383</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2383</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2383</v>
       </c>
       <c r="I49" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2383</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2383</v>
       </c>
       <c r="N49" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0184</v>
+        <v>0.1479</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0117</v>
+        <v>0.094</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4288</v>
+        <v>-0.385</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0184</v>
+        <v>0.1479</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0184</v>
+        <v>0.1479</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0184</v>
+        <v>0.1479</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0184</v>
+        <v>0.1479</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>162</v>
+        <v>235</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0184</v>
+        <v>0.1479</v>
       </c>
       <c r="N50" t="n">
-        <v>162</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0423</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0269</v>
+        <v>0.0556</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4385</v>
+        <v>-0.4091</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0423</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0423</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0423</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0423</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>214</v>
+        <v>119</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0423</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>214</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1498</v>
+        <v>0.0803</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.0511</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4819</v>
+        <v>-0.4119</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1498</v>
+        <v>0.0803</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1498</v>
+        <v>0.0803</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1498</v>
+        <v>0.0803</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1498</v>
+        <v>0.0803</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>162</v>
+        <v>235</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1498</v>
+        <v>0.0803</v>
       </c>
       <c r="N52" t="n">
-        <v>162</v>
+        <v>235</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0985</v>
+        <v>0.0464</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4839</v>
+        <v>-0.4149</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>235</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2138</v>
+        <v>-0.0184</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1359</v>
+        <v>-0.0117</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5077</v>
+        <v>-0.4512</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2138</v>
+        <v>-0.0184</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2138</v>
+        <v>-0.0184</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2138</v>
+        <v>-0.0184</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2138</v>
+        <v>-0.0184</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2138</v>
+        <v>-0.0184</v>
       </c>
       <c r="N54" t="n">
-        <v>235</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2683</v>
+        <v>-0.1498</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1706</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5036</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2683</v>
+        <v>-0.1498</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2756</v>
+        <v>-0.1498</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0073</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2756</v>
+        <v>-0.1498</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2756</v>
+        <v>-0.1498</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0073</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="L55" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2683</v>
+        <v>-0.1498</v>
       </c>
       <c r="N55" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2886</v>
+        <v>-0.2138</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1835</v>
+        <v>-0.1359</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.538</v>
+        <v>-0.5291</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2886</v>
+        <v>-0.2138</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2886</v>
+        <v>-0.2138</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2886</v>
+        <v>-0.2138</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2886</v>
+        <v>-0.2138</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2886</v>
+        <v>-0.2138</v>
       </c>
       <c r="N56" t="n">
-        <v>119</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2953</v>
+        <v>-0.2683</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1878</v>
+        <v>-0.1706</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5407</v>
+        <v>-0.5508</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2953</v>
+        <v>-0.2683</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2953</v>
+        <v>-0.2756</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.0073</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2953</v>
+        <v>-0.2756</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2953</v>
+        <v>-0.2756</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.0073</v>
       </c>
       <c r="K57" t="n">
-        <v>235</v>
+        <v>94</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2953</v>
+        <v>-0.2683</v>
       </c>
       <c r="N57" t="n">
-        <v>235</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58">
@@ -3078,7 +3078,7 @@
         <v>-0.1971</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5466</v>
+        <v>-0.5674</v>
       </c>
       <c r="E58" t="n">
         <v>-0.31</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2541</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5828</v>
+        <v>-0.6031</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3996</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2567</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5845</v>
+        <v>-0.6048</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4038</v>
@@ -3216,7 +3216,7 @@
         <v>-0.4777</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7249</v>
+        <v>-0.7432</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7513</v>
@@ -3262,7 +3262,7 @@
         <v>-0.4847</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7294</v>
+        <v>-0.7477</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7624</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4866</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7306</v>
+        <v>-0.7488</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7654</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5802</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.79</v>
+        <v>-0.8075</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9126</v>
@@ -3400,7 +3400,7 @@
         <v>-0.614</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8115</v>
+        <v>-0.8286</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9657</v>
@@ -3446,7 +3446,7 @@
         <v>-0.8284</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9477</v>
+        <v>-0.963</v>
       </c>
       <c r="E66" t="n">
         <v>-1.3029</v>
@@ -3492,7 +3492,7 @@
         <v>-0.868</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9729</v>
+        <v>-0.9878</v>
       </c>
       <c r="E67" t="n">
         <v>-1.3652</v>
@@ -3538,7 +3538,7 @@
         <v>-0.8917</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9879</v>
+        <v>-1.0026</v>
       </c>
       <c r="E68" t="n">
         <v>-1.4024</v>
@@ -3584,7 +3584,7 @@
         <v>-0.9177999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0045</v>
+        <v>-1.019</v>
       </c>
       <c r="E69" t="n">
         <v>-1.4435</v>
@@ -3630,7 +3630,7 @@
         <v>-0.9364</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0163</v>
+        <v>-1.0307</v>
       </c>
       <c r="E70" t="n">
         <v>-1.4728</v>
@@ -3676,7 +3676,7 @@
         <v>-0.9372</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0168</v>
+        <v>-1.0312</v>
       </c>
       <c r="E71" t="n">
         <v>-1.474</v>
@@ -3722,7 +3722,7 @@
         <v>-0.9422</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.02</v>
+        <v>-1.0343</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4819</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9451000000000001</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0218</v>
+        <v>-1.0361</v>
       </c>
       <c r="E73" t="n">
         <v>-1.4864</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.5463</v>
+        <v>-1.5441</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.9831</v>
+        <v>-0.9817</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.046</v>
+        <v>-1.0591</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.5463</v>
+        <v>-1.5441</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5931</v>
       </c>
       <c r="G74" t="n">
         <v>-0.951</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5931</v>
       </c>
       <c r="I74" t="n">
         <v>-0.5981</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.7682</v>
+        <v>-1.5856</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.1242</v>
+        <v>-1.0081</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1357</v>
+        <v>-1.0756</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.7682</v>
+        <v>-1.5856</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7682</v>
+        <v>-0.5856</v>
       </c>
       <c r="G75" t="n">
         <v>-1</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7682</v>
+        <v>-0.5856</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7682</v>
+        <v>-0.5856</v>
       </c>
       <c r="J75" t="n">
         <v>-1</v>
@@ -3887,7 +3887,7 @@
         <v>78</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.7682</v>
+        <v>-1.5856</v>
       </c>
       <c r="N75" t="n">
         <v>222</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.4001</v>
+        <v>-2.3947</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.526</v>
+        <v>-1.5226</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3909</v>
+        <v>-1.398</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.4001</v>
+        <v>-2.3947</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.453</v>
+        <v>-1.4476</v>
       </c>
       <c r="G76" t="n">
         <v>-0.9471000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.453</v>
+        <v>-1.4476</v>
       </c>
       <c r="I76" t="n">
         <v>-1.4598</v>
@@ -3952,7 +3952,7 @@
         <v>-1.5303</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3937</v>
+        <v>-1.4028</v>
       </c>
       <c r="E77" t="n">
         <v>-2.4068</v>
@@ -3998,7 +3998,7 @@
         <v>-1.654</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4723</v>
+        <v>-1.4803</v>
       </c>
       <c r="E78" t="n">
         <v>-2.6014</v>
@@ -4044,7 +4044,7 @@
         <v>-1.8044</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5679</v>
+        <v>-1.5746</v>
       </c>
       <c r="E79" t="n">
         <v>-2.838</v>
@@ -4090,7 +4090,7 @@
         <v>-1.9308</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6482</v>
+        <v>-1.6538</v>
       </c>
       <c r="E80" t="n">
         <v>-3.0368</v>
@@ -4136,7 +4136,7 @@
         <v>-2.1912</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8136</v>
+        <v>-1.8169</v>
       </c>
       <c r="E81" t="n">
         <v>-3.4463</v>
